--- a/informes_data/Euroleague/2025-26/playoffs/aggregate_individual/AGG_IND_OLYMPIACOS PIRAEUS.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/aggregate_individual/AGG_IND_OLYMPIACOS PIRAEUS.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X15"/>
+  <dimension ref="A1:X16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -565,13 +565,13 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>31.6647</v>
+        <v>30.4241</v>
       </c>
       <c r="E2" t="n">
-        <v>20.7964</v>
+        <v>20.9132</v>
       </c>
       <c r="F2" t="n">
-        <v>10.8684</v>
+        <v>9.5108</v>
       </c>
       <c r="G2" t="n">
         <v>20.2897</v>
@@ -610,13 +610,13 @@
         <v>6.1417</v>
       </c>
       <c r="S2" t="n">
-        <v>4.8291</v>
+        <v>3.5882</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8386</v>
+        <v>0.9553</v>
       </c>
       <c r="U2" t="n">
-        <v>3.9906</v>
+        <v>2.6331</v>
       </c>
       <c r="V2" t="n">
         <v>4.0438</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>N. MILUTINOV</t>
+          <t>E. FOURNIER</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>23.5354</v>
+        <v>21.1716</v>
       </c>
       <c r="E3" t="n">
-        <v>14.203</v>
+        <v>8.0907</v>
       </c>
       <c r="F3" t="n">
-        <v>9.3323</v>
+        <v>13.0809</v>
       </c>
       <c r="G3" t="n">
-        <v>6.1821</v>
+        <v>20.7128</v>
       </c>
       <c r="H3" t="n">
-        <v>1.1845</v>
+        <v>0.8606999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>4.9975</v>
+        <v>19.852</v>
       </c>
       <c r="J3" t="n">
-        <v>5.5641</v>
+        <v>16.8282</v>
       </c>
       <c r="K3" t="n">
-        <v>2.3604</v>
+        <v>3.7788</v>
       </c>
       <c r="L3" t="n">
-        <v>3.2037</v>
+        <v>13.0493</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6180000000000001</v>
+        <v>3.8847</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.1759</v>
+        <v>-2.918</v>
       </c>
       <c r="O3" t="n">
-        <v>1.7939</v>
+        <v>6.8026</v>
       </c>
       <c r="P3" t="n">
-        <v>3.1847</v>
+        <v>-5.0044</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.7298</v>
+        <v>-12.7385</v>
       </c>
       <c r="R3" t="n">
-        <v>5.9143</v>
+        <v>7.734100000000001</v>
       </c>
       <c r="S3" t="n">
-        <v>12.9901</v>
+        <v>3.9864</v>
       </c>
       <c r="T3" t="n">
-        <v>9.1</v>
+        <v>-0.1312</v>
       </c>
       <c r="U3" t="n">
-        <v>3.8901</v>
+        <v>4.1175</v>
       </c>
       <c r="V3" t="n">
-        <v>1.1784</v>
+        <v>1.4767</v>
       </c>
       <c r="W3" t="n">
-        <v>2.2685</v>
+        <v>4.132</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0901</v>
+        <v>-2.6552</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E. FOURNIER</t>
+          <t>T. WALKUP</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>19.4188</v>
+        <v>18.7917</v>
       </c>
       <c r="E4" t="n">
-        <v>6.0792</v>
+        <v>13.6356</v>
       </c>
       <c r="F4" t="n">
-        <v>13.3396</v>
+        <v>5.1562</v>
       </c>
       <c r="G4" t="n">
-        <v>20.7128</v>
+        <v>18.5157</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8606999999999999</v>
+        <v>2.0346</v>
       </c>
       <c r="I4" t="n">
-        <v>19.852</v>
+        <v>16.4811</v>
       </c>
       <c r="J4" t="n">
-        <v>16.8282</v>
+        <v>20.2367</v>
       </c>
       <c r="K4" t="n">
-        <v>3.7788</v>
+        <v>5.0876</v>
       </c>
       <c r="L4" t="n">
-        <v>13.0493</v>
+        <v>15.1491</v>
       </c>
       <c r="M4" t="n">
-        <v>3.8847</v>
+        <v>-1.721</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.918</v>
+        <v>-3.053</v>
       </c>
       <c r="O4" t="n">
-        <v>6.8026</v>
+        <v>1.3321</v>
       </c>
       <c r="P4" t="n">
-        <v>-5.0044</v>
+        <v>-0.6825</v>
       </c>
       <c r="Q4" t="n">
-        <v>-12.7385</v>
+        <v>-7.279199999999999</v>
       </c>
       <c r="R4" t="n">
-        <v>7.734100000000001</v>
+        <v>6.5968</v>
       </c>
       <c r="S4" t="n">
-        <v>2.2337</v>
+        <v>1.4335</v>
       </c>
       <c r="T4" t="n">
-        <v>-2.1424</v>
+        <v>-1.6605</v>
       </c>
       <c r="U4" t="n">
-        <v>4.3761</v>
+        <v>3.094</v>
       </c>
       <c r="V4" t="n">
-        <v>1.4767</v>
+        <v>-0.4749999999999998</v>
       </c>
       <c r="W4" t="n">
-        <v>4.132</v>
+        <v>2.3385</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.6552</v>
+        <v>-2.8136</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T. WALKUP</t>
+          <t>N. MILUTINOV</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>14.8679</v>
+        <v>15.8938</v>
       </c>
       <c r="E5" t="n">
-        <v>10.5197</v>
+        <v>7.3695</v>
       </c>
       <c r="F5" t="n">
-        <v>4.348</v>
+        <v>8.5243</v>
       </c>
       <c r="G5" t="n">
-        <v>18.5157</v>
+        <v>6.1821</v>
       </c>
       <c r="H5" t="n">
-        <v>2.0346</v>
+        <v>1.1845</v>
       </c>
       <c r="I5" t="n">
-        <v>16.4811</v>
+        <v>4.9975</v>
       </c>
       <c r="J5" t="n">
-        <v>20.2367</v>
+        <v>5.5641</v>
       </c>
       <c r="K5" t="n">
-        <v>5.0876</v>
+        <v>2.3604</v>
       </c>
       <c r="L5" t="n">
-        <v>15.1491</v>
+        <v>3.2037</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.721</v>
+        <v>0.6180000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>-3.053</v>
+        <v>-1.1759</v>
       </c>
       <c r="O5" t="n">
-        <v>1.3321</v>
+        <v>1.7939</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.6825</v>
+        <v>3.1847</v>
       </c>
       <c r="Q5" t="n">
-        <v>-7.279199999999999</v>
+        <v>-2.7298</v>
       </c>
       <c r="R5" t="n">
-        <v>6.5968</v>
+        <v>5.9143</v>
       </c>
       <c r="S5" t="n">
-        <v>-2.4903</v>
+        <v>5.3486</v>
       </c>
       <c r="T5" t="n">
-        <v>-4.7764</v>
+        <v>2.2665</v>
       </c>
       <c r="U5" t="n">
-        <v>2.286</v>
+        <v>3.0821</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.4749999999999998</v>
+        <v>1.1784</v>
       </c>
       <c r="W5" t="n">
-        <v>2.3385</v>
+        <v>2.2685</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.8136</v>
+        <v>-1.0901</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. HALL</t>
+          <t>C. JOSEPH</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>10.6832</v>
+        <v>9.386000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>6.279</v>
+        <v>1.9404</v>
       </c>
       <c r="F6" t="n">
-        <v>4.4044</v>
+        <v>7.4455</v>
       </c>
       <c r="G6" t="n">
-        <v>5.0301</v>
+        <v>8.6896</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3994</v>
+        <v>0.7246999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>4.6306</v>
+        <v>7.9651</v>
       </c>
       <c r="J6" t="n">
-        <v>5.1606</v>
+        <v>7.0354</v>
       </c>
       <c r="K6" t="n">
-        <v>3.1861</v>
+        <v>1.576</v>
       </c>
       <c r="L6" t="n">
-        <v>1.9745</v>
+        <v>5.4593</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1304</v>
+        <v>1.6543</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.7867</v>
+        <v>-0.8513999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>2.6563</v>
+        <v>2.5057</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6824000000000001</v>
+        <v>-2.2747</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.2748</v>
+        <v>-8.189</v>
       </c>
       <c r="R6" t="n">
-        <v>2.9571</v>
+        <v>5.9143</v>
       </c>
       <c r="S6" t="n">
-        <v>6.5177</v>
+        <v>1.266</v>
       </c>
       <c r="T6" t="n">
-        <v>3.3049</v>
+        <v>-0.1761</v>
       </c>
       <c r="U6" t="n">
-        <v>3.2128</v>
+        <v>1.4421</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.5469</v>
+        <v>1.7053</v>
       </c>
       <c r="W6" t="n">
-        <v>0.08830000000000005</v>
+        <v>3.2704</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.6352</v>
+        <v>-1.5651</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C. JOSEPH</t>
+          <t>S. MCKISSIC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>7.2076</v>
+        <v>8.1945</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1175000000000002</v>
+        <v>7.3818</v>
       </c>
       <c r="F7" t="n">
-        <v>7.0899</v>
+        <v>0.8129000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>8.6896</v>
+        <v>7.3665</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7246999999999999</v>
+        <v>0.7411999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>7.9651</v>
+        <v>6.6254</v>
       </c>
       <c r="J7" t="n">
-        <v>7.0354</v>
+        <v>7.311900000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>1.576</v>
+        <v>2.5976</v>
       </c>
       <c r="L7" t="n">
-        <v>5.4593</v>
+        <v>4.7142</v>
       </c>
       <c r="M7" t="n">
-        <v>1.6543</v>
+        <v>0.05460000000000019</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8513999999999999</v>
+        <v>-1.8566</v>
       </c>
       <c r="O7" t="n">
-        <v>2.5057</v>
+        <v>1.9112</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.2747</v>
+        <v>1.3648</v>
       </c>
       <c r="Q7" t="n">
-        <v>-8.189</v>
+        <v>-1.1374</v>
       </c>
       <c r="R7" t="n">
-        <v>5.9143</v>
+        <v>2.5022</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9124999999999999</v>
+        <v>0.3950000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.9991</v>
+        <v>-0.5863</v>
       </c>
       <c r="U7" t="n">
-        <v>1.0865</v>
+        <v>0.9814000000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>1.7053</v>
+        <v>-0.9317000000000001</v>
       </c>
       <c r="W7" t="n">
-        <v>3.2704</v>
+        <v>1.7935</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.5651</v>
+        <v>-2.7253</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. MCKISSIC</t>
+          <t>S. VEZENKOV</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>6.671799999999999</v>
+        <v>7.849</v>
       </c>
       <c r="E8" t="n">
-        <v>6.376</v>
+        <v>3.557799999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2957000000000002</v>
+        <v>4.2912</v>
       </c>
       <c r="G8" t="n">
-        <v>7.3665</v>
+        <v>5.616100000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7411999999999999</v>
+        <v>-1.2864</v>
       </c>
       <c r="I8" t="n">
-        <v>6.6254</v>
+        <v>6.9024</v>
       </c>
       <c r="J8" t="n">
-        <v>7.311900000000001</v>
+        <v>9.4223</v>
       </c>
       <c r="K8" t="n">
-        <v>2.5976</v>
+        <v>1.956</v>
       </c>
       <c r="L8" t="n">
-        <v>4.7142</v>
+        <v>7.466200000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>0.05460000000000019</v>
+        <v>-3.8061</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.8566</v>
+        <v>-3.2424</v>
       </c>
       <c r="O8" t="n">
-        <v>1.9112</v>
+        <v>-0.5637000000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>1.3648</v>
+        <v>9.999999999987796e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1374</v>
+        <v>-7.279100000000001</v>
       </c>
       <c r="R8" t="n">
-        <v>2.5022</v>
+        <v>7.2791</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.1279</v>
+        <v>2.3913</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.592</v>
+        <v>-1.4688</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4642000000000001</v>
+        <v>3.8603</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.9317000000000001</v>
+        <v>-0.1583</v>
       </c>
       <c r="W8" t="n">
-        <v>1.7935</v>
+        <v>2.8837</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.7253</v>
+        <v>-3.042</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. VEZENKOV</t>
+          <t>D. HALL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>6.403300000000002</v>
+        <v>7.4041</v>
       </c>
       <c r="E9" t="n">
-        <v>1.3041</v>
+        <v>3.7109</v>
       </c>
       <c r="F9" t="n">
-        <v>5.0992</v>
+        <v>3.693300000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>5.616100000000001</v>
+        <v>5.0301</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.2864</v>
+        <v>0.3994</v>
       </c>
       <c r="I9" t="n">
-        <v>6.9024</v>
+        <v>4.6306</v>
       </c>
       <c r="J9" t="n">
-        <v>9.4223</v>
+        <v>5.1606</v>
       </c>
       <c r="K9" t="n">
-        <v>1.956</v>
+        <v>3.1861</v>
       </c>
       <c r="L9" t="n">
-        <v>7.466200000000001</v>
+        <v>1.9745</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.8061</v>
+        <v>-0.1304</v>
       </c>
       <c r="N9" t="n">
-        <v>-3.2424</v>
+        <v>-2.7867</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.5637000000000001</v>
+        <v>2.6563</v>
       </c>
       <c r="P9" t="n">
-        <v>9.999999999987796e-05</v>
+        <v>0.6824000000000001</v>
       </c>
       <c r="Q9" t="n">
-        <v>-7.279100000000001</v>
+        <v>-2.2748</v>
       </c>
       <c r="R9" t="n">
-        <v>7.2791</v>
+        <v>2.9571</v>
       </c>
       <c r="S9" t="n">
-        <v>0.9455000000000002</v>
+        <v>3.2384</v>
       </c>
       <c r="T9" t="n">
-        <v>-3.7226</v>
+        <v>0.7366999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>4.6682</v>
+        <v>2.5017</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1583</v>
+        <v>-1.5469</v>
       </c>
       <c r="W9" t="n">
-        <v>2.8837</v>
+        <v>0.08830000000000005</v>
       </c>
       <c r="X9" t="n">
-        <v>-3.042</v>
+        <v>-1.6352</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>2.2128</v>
+        <v>1.8519</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.577</v>
+        <v>-0.7118000000000002</v>
       </c>
       <c r="F10" t="n">
-        <v>2.7898</v>
+        <v>2.5636</v>
       </c>
       <c r="G10" t="n">
         <v>-0.2606000000000001</v>
@@ -1234,13 +1234,13 @@
         <v>3.6396</v>
       </c>
       <c r="S10" t="n">
-        <v>1.4534</v>
+        <v>1.0924</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3475000000000001</v>
+        <v>0.2127</v>
       </c>
       <c r="U10" t="n">
-        <v>1.1059</v>
+        <v>0.8797999999999999</v>
       </c>
       <c r="V10" t="n">
         <v>1.0201</v>
@@ -1267,13 +1267,13 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>1.5989</v>
+        <v>1.1049</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.2644</v>
+        <v>-1.0815</v>
       </c>
       <c r="F11" t="n">
-        <v>1.8632</v>
+        <v>2.1865</v>
       </c>
       <c r="G11" t="n">
         <v>4.9978</v>
@@ -1312,13 +1312,13 @@
         <v>1.5923</v>
       </c>
       <c r="S11" t="n">
-        <v>1.8558</v>
+        <v>1.3618</v>
       </c>
       <c r="T11" t="n">
-        <v>1.3532</v>
+        <v>0.5359999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5027</v>
+        <v>0.8258000000000001</v>
       </c>
       <c r="V11" t="n">
         <v>-1.1601</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>F. NTILIKINA</t>
+          <t>M. MORRIS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.8727</v>
+        <v>0.1167</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.2634</v>
+        <v>0.1167</v>
       </c>
       <c r="F12" t="n">
-        <v>1.3907</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.4576</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2089</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.6665</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.1022</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1208</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.223</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1.6446</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>0.0881</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>1.5565</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.3648</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3648</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3784</v>
+        <v>0.1167</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2036</v>
+        <v>0.1167</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1748</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.7935</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.7935</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>K. PAPANIKOLAOU</t>
+          <t>F. NTILIKINA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.42</v>
+        <v>-1.413</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.1044</v>
+        <v>-3.1916</v>
       </c>
       <c r="F13" t="n">
-        <v>1.6843</v>
+        <v>1.7785</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.4547</v>
+        <v>-0.4576</v>
       </c>
       <c r="H13" t="n">
-        <v>0.4609000000000001</v>
+        <v>0.2089</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.9156</v>
+        <v>-0.6665</v>
       </c>
       <c r="J13" t="n">
-        <v>1.6897</v>
+        <v>-2.1022</v>
       </c>
       <c r="K13" t="n">
-        <v>1.8806</v>
+        <v>0.1208</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.1911</v>
+        <v>-2.223</v>
       </c>
       <c r="M13" t="n">
-        <v>-3.1444</v>
+        <v>1.6446</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.4197</v>
+        <v>0.0881</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.7248</v>
+        <v>1.5565</v>
       </c>
       <c r="P13" t="n">
-        <v>1.1374</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-5.0044</v>
+        <v>-1.3648</v>
       </c>
       <c r="R13" t="n">
-        <v>6.1418</v>
+        <v>1.3648</v>
       </c>
       <c r="S13" t="n">
-        <v>0.6227000000000003</v>
+        <v>0.8381</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7897000000000001</v>
+        <v>0.2755</v>
       </c>
       <c r="U13" t="n">
-        <v>1.4123</v>
+        <v>0.5626</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.7253</v>
+        <v>-1.7935</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.7253</v>
+        <v>-1.7935</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>T. DORSEY</t>
+          <t>K. PAPANIKOLAOU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>-14.4026</v>
+        <v>-1.6928</v>
       </c>
       <c r="E14" t="n">
-        <v>-15.5372</v>
+        <v>-3.862</v>
       </c>
       <c r="F14" t="n">
-        <v>1.1346</v>
+        <v>2.1692</v>
       </c>
       <c r="G14" t="n">
-        <v>-10.6309</v>
+        <v>-1.4547</v>
       </c>
       <c r="H14" t="n">
-        <v>-4.8066</v>
+        <v>0.4609000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-5.8243</v>
+        <v>-1.9156</v>
       </c>
       <c r="J14" t="n">
-        <v>-6.6897</v>
+        <v>1.6897</v>
       </c>
       <c r="K14" t="n">
-        <v>-2.8019</v>
+        <v>1.8806</v>
       </c>
       <c r="L14" t="n">
-        <v>-3.8878</v>
+        <v>-0.1911</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.9413</v>
+        <v>-3.1444</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.0047</v>
+        <v>-1.4197</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.9366</v>
+        <v>-1.7248</v>
       </c>
       <c r="P14" t="n">
-        <v>-2.5022</v>
+        <v>1.1374</v>
       </c>
       <c r="Q14" t="n">
-        <v>-7.2792</v>
+        <v>-5.0044</v>
       </c>
       <c r="R14" t="n">
-        <v>4.776899999999999</v>
+        <v>6.1418</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.993</v>
+        <v>1.35</v>
       </c>
       <c r="T14" t="n">
-        <v>-3.2919</v>
+        <v>-0.5473</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2989000000000001</v>
+        <v>1.8971</v>
       </c>
       <c r="V14" t="n">
-        <v>1.7235</v>
+        <v>-2.7253</v>
       </c>
       <c r="W14" t="n">
-        <v>1.7235</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-2.7253</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>T. DORSEY</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,66 +1579,144 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>105.5691</v>
+        <v>-10.9995</v>
       </c>
       <c r="E15" t="n">
-        <v>41.92850000000001</v>
+        <v>-13.4271</v>
       </c>
       <c r="F15" t="n">
-        <v>63.6401</v>
+        <v>2.4275</v>
       </c>
       <c r="G15" t="n">
+        <v>-10.6309</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-4.8066</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-5.8243</v>
+      </c>
+      <c r="J15" t="n">
+        <v>-6.6897</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-2.8019</v>
+      </c>
+      <c r="L15" t="n">
+        <v>-3.8878</v>
+      </c>
+      <c r="M15" t="n">
+        <v>-3.9413</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-2.0047</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-1.9366</v>
+      </c>
+      <c r="P15" t="n">
+        <v>-2.5022</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>-7.2792</v>
+      </c>
+      <c r="R15" t="n">
+        <v>4.776899999999999</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.4101</v>
+      </c>
+      <c r="T15" t="n">
+        <v>-1.1818</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.5918</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.7235</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.7235</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>OLYMPIACOS PIRAEUS</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>5</v>
+      </c>
+      <c r="D16" t="n">
+        <v>108.083</v>
+      </c>
+      <c r="E16" t="n">
+        <v>44.44259999999998</v>
+      </c>
+      <c r="F16" t="n">
+        <v>63.64040000000001</v>
+      </c>
+      <c r="G16" t="n">
         <v>84.59660000000001</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H16" t="n">
         <v>8.457799999999999</v>
       </c>
-      <c r="I15" t="n">
+      <c r="I16" t="n">
         <v>76.1388</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J16" t="n">
         <v>86.48660000000001</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K16" t="n">
         <v>30.3146</v>
       </c>
-      <c r="L15" t="n">
+      <c r="L16" t="n">
         <v>56.17140000000001</v>
       </c>
-      <c r="M15" t="n">
+      <c r="M16" t="n">
         <v>-1.889599999999998</v>
       </c>
-      <c r="N15" t="n">
+      <c r="N16" t="n">
         <v>-21.8569</v>
       </c>
-      <c r="O15" t="n">
+      <c r="O16" t="n">
         <v>19.9671</v>
       </c>
-      <c r="P15" t="n">
-        <v>-5.686800000000002</v>
-      </c>
-      <c r="Q15" t="n">
+      <c r="P16" t="n">
+        <v>-5.6868</v>
+      </c>
+      <c r="Q16" t="n">
         <v>-68.2423</v>
       </c>
-      <c r="R15" t="n">
+      <c r="R16" t="n">
         <v>62.55500000000001</v>
       </c>
-      <c r="S15" t="n">
-        <v>24.30270000000001</v>
-      </c>
-      <c r="T15" t="n">
-        <v>-3.166300000000001</v>
-      </c>
-      <c r="U15" t="n">
-        <v>27.4691</v>
-      </c>
-      <c r="V15" t="n">
-        <v>2.357</v>
-      </c>
-      <c r="W15" t="n">
+      <c r="S16" t="n">
+        <v>26.8165</v>
+      </c>
+      <c r="T16" t="n">
+        <v>-0.6526</v>
+      </c>
+      <c r="U16" t="n">
+        <v>27.4693</v>
+      </c>
+      <c r="V16" t="n">
+        <v>2.357000000000002</v>
+      </c>
+      <c r="W16" t="n">
         <v>26.8509</v>
       </c>
-      <c r="X15" t="n">
+      <c r="X16" t="n">
         <v>-24.4941</v>
       </c>
     </row>
